--- a/data/trans_dic/P37-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P37-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha vacunado de la gripe en la última campaña</t>
+          <t>Población que se ha vacunado de la gripe en la última campaña (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,71; 18,15</t>
+          <t>12,87; 18,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,37; 23,34</t>
+          <t>17,35; 23,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 20,08</t>
+          <t>14,49; 20,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,36; 35,44</t>
+          <t>27,97; 35,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 17,88</t>
+          <t>12,13; 17,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,16; 21,96</t>
+          <t>16,07; 22,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,07; 21,06</t>
+          <t>14,8; 20,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,11; 40,88</t>
+          <t>34,98; 40,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,31; 17,04</t>
+          <t>13,07; 17,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,66; 21,84</t>
+          <t>17,52; 21,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,32; 19,42</t>
+          <t>15,49; 19,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,48; 37,06</t>
+          <t>32,34; 37,21</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,75; 16,31</t>
+          <t>11,86; 16,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,43; 20,35</t>
+          <t>15,2; 20,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,53; 16,79</t>
+          <t>12,42; 16,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 27,95</t>
+          <t>10,22; 28,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,08; 18,98</t>
+          <t>13,85; 18,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,39; 21,48</t>
+          <t>16,08; 21,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,71; 21,06</t>
+          <t>15,36; 20,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,31; 38,45</t>
+          <t>33,37; 38,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,62; 16,84</t>
+          <t>13,48; 16,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,38; 19,93</t>
+          <t>16,4; 19,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 18,13</t>
+          <t>14,61; 18,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,07; 32,19</t>
+          <t>18,53; 32,09</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,53; 15,69</t>
+          <t>10,43; 15,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,21; 18,68</t>
+          <t>13,03; 18,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,92; 19,58</t>
+          <t>14,01; 19,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,49; 33,64</t>
+          <t>26,12; 33,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,33; 18,94</t>
+          <t>13,37; 19,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,4; 20,11</t>
+          <t>14,48; 20,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 18,83</t>
+          <t>13,02; 18,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,15; 70,22</t>
+          <t>30,11; 73,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,69; 16,58</t>
+          <t>12,65; 16,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 18,43</t>
+          <t>14,47; 18,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,27; 18,24</t>
+          <t>14,34; 18,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,37; 60,45</t>
+          <t>29,56; 58,57</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 15,58</t>
+          <t>11,44; 15,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,97; 19,93</t>
+          <t>14,85; 20,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,23; 17,87</t>
+          <t>13,05; 17,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,69; 39,1</t>
+          <t>33,08; 39,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 18,26</t>
+          <t>13,67; 18,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,83; 20,58</t>
+          <t>15,95; 20,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,17; 20,27</t>
+          <t>14,95; 20,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,77; 39,49</t>
+          <t>29,69; 39,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,3; 16,46</t>
+          <t>13,12; 16,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,96; 19,58</t>
+          <t>16,09; 19,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 18,5</t>
+          <t>14,95; 18,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,64; 38,39</t>
+          <t>31,79; 38,46</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,68; 14,97</t>
+          <t>12,76; 14,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,36; 19,13</t>
+          <t>16,42; 19,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,53; 17,12</t>
+          <t>14,64; 17,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,33; 31,85</t>
+          <t>22,0; 31,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 17,08</t>
+          <t>14,63; 17,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,95; 19,61</t>
+          <t>16,97; 19,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,93; 18,62</t>
+          <t>16,03; 18,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,91; 50,92</t>
+          <t>34,77; 49,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,07; 15,81</t>
+          <t>14,03; 15,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,03; 18,89</t>
+          <t>16,91; 18,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 17,43</t>
+          <t>15,65; 17,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,79; 40,34</t>
+          <t>31,01; 40,25</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha vacunado de la gripe en la última campaña</t>
+          <t>Población que se ha vacunado de la gripe en la última campaña (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>88198; 125997</t>
+          <t>89337; 127375</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122007; 163918</t>
+          <t>121851; 165520</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98255; 135525</t>
+          <t>97776; 135793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>180195; 225214</t>
+          <t>177703; 224456</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>85552; 122942</t>
+          <t>83367; 120756</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>112629; 153098</t>
+          <t>111995; 155036</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>101393; 141725</t>
+          <t>99607; 139958</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>237153; 276099</t>
+          <t>236220; 273629</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>183856; 235352</t>
+          <t>180526; 235485</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>247095; 305660</t>
+          <t>245220; 303989</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>206442; 261710</t>
+          <t>208760; 262241</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>425743; 485802</t>
+          <t>423896; 487781</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>112966; 156830</t>
+          <t>114111; 157296</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>157076; 207122</t>
+          <t>154712; 204455</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128096; 171652</t>
+          <t>126992; 168942</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>136796; 333366</t>
+          <t>121932; 336549</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>136353; 183840</t>
+          <t>134080; 183121</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>168969; 221527</t>
+          <t>165846; 221269</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>163825; 219666</t>
+          <t>160217; 214477</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>319185; 368415</t>
+          <t>319719; 367975</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>262886; 325112</t>
+          <t>260265; 327378</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>335541; 408342</t>
+          <t>336098; 408625</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>301619; 374495</t>
+          <t>301833; 372419</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>410220; 692452</t>
+          <t>398484; 690172</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71338; 106336</t>
+          <t>70692; 106417</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>99960; 141336</t>
+          <t>98600; 142957</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105738; 148756</t>
+          <t>106400; 149612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>186690; 237049</t>
+          <t>184096; 235680</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>91030; 129348</t>
+          <t>91308; 130458</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>111885; 156312</t>
+          <t>112573; 157259</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>103492; 147819</t>
+          <t>102235; 148027</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>281411; 655423</t>
+          <t>281024; 684962</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>172606; 225550</t>
+          <t>172056; 225306</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>219920; 282754</t>
+          <t>221989; 285226</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>220369; 281653</t>
+          <t>221502; 282110</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>497413; 990182</t>
+          <t>484135; 959421</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>107954; 146708</t>
+          <t>107717; 148747</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>141437; 188254</t>
+          <t>140276; 189903</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124064; 167524</t>
+          <t>122313; 165634</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>302969; 362349</t>
+          <t>306608; 367671</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>142348; 189625</t>
+          <t>141972; 190592</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>166468; 216446</t>
+          <t>167770; 217708</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>158327; 211548</t>
+          <t>156075; 210376</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>314339; 431440</t>
+          <t>324400; 436301</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>263272; 326001</t>
+          <t>259818; 320656</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>318725; 390853</t>
+          <t>321255; 392387</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>294437; 366452</t>
+          <t>296146; 364532</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>638870; 775355</t>
+          <t>642055; 776731</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>415220; 490166</t>
+          <t>417913; 490096</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559635; 654722</t>
+          <t>561934; 651223</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>493254; 581097</t>
+          <t>496907; 576882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>772581; 1102113</t>
+          <t>761251; 1094074</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>491392; 576847</t>
+          <t>494083; 574991</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>602855; 697599</t>
+          <t>603682; 697331</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>564712; 659929</t>
+          <t>568059; 664023</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1277459; 1863471</t>
+          <t>1272239; 1826627</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>936157; 1051755</t>
+          <t>933527; 1045896</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1188426; 1318334</t>
+          <t>1180465; 1318056</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1079768; 1209766</t>
+          <t>1085633; 1210414</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2191821; 2871650</t>
+          <t>2207379; 2865676</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P37-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P37-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,87; 18,35</t>
+          <t>12,52; 18,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,35; 23,56</t>
+          <t>17,35; 23,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,49; 20,12</t>
+          <t>14,29; 20,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,97; 35,32</t>
+          <t>28,94; 35,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 17,57</t>
+          <t>12,31; 17,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,07; 22,24</t>
+          <t>16,34; 22,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,8; 20,8</t>
+          <t>14,91; 20,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,98; 40,52</t>
+          <t>34,65; 40,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,07; 17,05</t>
+          <t>13,18; 16,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,52; 21,72</t>
+          <t>17,31; 21,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,49; 19,46</t>
+          <t>15,58; 19,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,34; 37,21</t>
+          <t>32,55; 37,05</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,86; 16,35</t>
+          <t>11,92; 16,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,2; 20,09</t>
+          <t>15,36; 20,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,42; 16,52</t>
+          <t>12,36; 16,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,22; 28,21</t>
+          <t>24,08; 29,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,85; 18,91</t>
+          <t>13,8; 18,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,08; 21,46</t>
+          <t>16,1; 20,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,36; 20,57</t>
+          <t>15,56; 20,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,37; 38,41</t>
+          <t>33,17; 38,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,48; 16,96</t>
+          <t>13,55; 16,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,4; 19,94</t>
+          <t>16,46; 19,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,61; 18,03</t>
+          <t>14,64; 17,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,53; 32,09</t>
+          <t>29,38; 33,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 15,71</t>
+          <t>10,56; 16,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,03; 18,89</t>
+          <t>13,06; 18,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,01; 19,7</t>
+          <t>13,82; 19,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,12; 33,45</t>
+          <t>26,16; 33,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,37; 19,1</t>
+          <t>13,36; 19,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,48; 20,23</t>
+          <t>14,4; 20,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,02; 18,86</t>
+          <t>12,91; 18,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,11; 73,39</t>
+          <t>29,24; 34,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,65; 16,56</t>
+          <t>12,6; 16,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,47; 18,6</t>
+          <t>14,49; 18,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 18,26</t>
+          <t>14,32; 17,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,56; 58,57</t>
+          <t>28,74; 33,17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,44; 15,8</t>
+          <t>11,32; 15,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,85; 20,1</t>
+          <t>14,99; 20,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,05; 17,67</t>
+          <t>12,98; 17,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,08; 39,67</t>
+          <t>32,27; 38,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,67; 18,35</t>
+          <t>13,77; 18,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,95; 20,7</t>
+          <t>15,87; 20,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 20,16</t>
+          <t>15,12; 20,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,69; 39,93</t>
+          <t>35,86; 40,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,12; 16,19</t>
+          <t>13,09; 16,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,09; 19,65</t>
+          <t>16,14; 19,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 18,4</t>
+          <t>14,8; 18,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,79; 38,46</t>
+          <t>35,09; 38,87</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,76; 14,97</t>
+          <t>12,72; 15,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,42; 19,03</t>
+          <t>16,35; 19,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 17,0</t>
+          <t>14,52; 16,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,0; 31,62</t>
+          <t>29,39; 32,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,63; 17,03</t>
+          <t>14,51; 17,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,97; 19,6</t>
+          <t>16,91; 19,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,03; 18,73</t>
+          <t>15,94; 18,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,77; 49,92</t>
+          <t>34,72; 37,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,03; 15,72</t>
+          <t>14,02; 15,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,91; 18,89</t>
+          <t>17,03; 18,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,65; 17,44</t>
+          <t>15,68; 17,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,01; 40,25</t>
+          <t>32,54; 34,59</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201201</t>
+          <t>222038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>255361</t>
+          <t>274383</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>456562</t>
+          <t>496420</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89337; 127375</t>
+          <t>86885; 127366</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>121851; 165520</t>
+          <t>121866; 164265</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97776; 135793</t>
+          <t>96398; 136406</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177703; 224456</t>
+          <t>199863; 248533</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83367; 120756</t>
+          <t>84612; 121108</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>111995; 155036</t>
+          <t>113885; 154912</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99607; 139958</t>
+          <t>100349; 141110</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>236220; 273629</t>
+          <t>253916; 295137</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>180526; 235485</t>
+          <t>182109; 233110</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>245220; 303989</t>
+          <t>242250; 305791</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>208760; 262241</t>
+          <t>209941; 263150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>423896; 487781</t>
+          <t>463374; 527391</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>257161</t>
+          <t>280440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>343350</t>
+          <t>381963</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>600511</t>
+          <t>662403</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>114111; 157296</t>
+          <t>114606; 158333</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>154712; 204455</t>
+          <t>156318; 207960</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126992; 168942</t>
+          <t>126361; 170552</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121932; 336549</t>
+          <t>252534; 312554</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>134080; 183121</t>
+          <t>133612; 182024</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>165846; 221269</t>
+          <t>165961; 216303</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>160217; 214477</t>
+          <t>162270; 215579</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>319719; 367975</t>
+          <t>355209; 410013</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>260265; 327378</t>
+          <t>261552; 324729</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>336098; 408625</t>
+          <t>337373; 406113</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>301833; 372419</t>
+          <t>302398; 370517</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>398484; 690172</t>
+          <t>622789; 702339</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210330</t>
+          <t>238834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>433928</t>
+          <t>259894</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>644258</t>
+          <t>498727</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70692; 106417</t>
+          <t>71567; 109408</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98600; 142957</t>
+          <t>98789; 143040</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106400; 149612</t>
+          <t>104946; 147770</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>184096; 235680</t>
+          <t>210069; 265814</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>91308; 130458</t>
+          <t>91218; 130307</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>112573; 157259</t>
+          <t>111882; 156827</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>102235; 148027</t>
+          <t>101378; 145522</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>281024; 684962</t>
+          <t>237535; 283368</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>172056; 225306</t>
+          <t>171418; 223991</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221989; 285226</t>
+          <t>222314; 287593</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>221502; 282110</t>
+          <t>221119; 277817</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>484135; 959421</t>
+          <t>464218; 535872</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334750</t>
+          <t>351124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>395937</t>
+          <t>427813</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>730687</t>
+          <t>778937</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>107717; 148747</t>
+          <t>106536; 149206</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>140276; 189903</t>
+          <t>141584; 191207</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>122313; 165634</t>
+          <t>121700; 165763</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>306608; 367671</t>
+          <t>319542; 381143</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>141972; 190592</t>
+          <t>143026; 191761</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>167770; 217708</t>
+          <t>166985; 219853</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>156075; 210376</t>
+          <t>157781; 209421</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>324400; 436301</t>
+          <t>401001; 454033</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>259818; 320656</t>
+          <t>259174; 324325</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>321255; 392387</t>
+          <t>322167; 389688</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>296146; 364532</t>
+          <t>293185; 363734</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>642055; 776731</t>
+          <t>739907; 819523</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1003443</t>
+          <t>1092435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1428576</t>
+          <t>1344053</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2432019</t>
+          <t>2436488</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>417913; 490096</t>
+          <t>416507; 494851</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561934; 651223</t>
+          <t>559303; 651651</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>496907; 576882</t>
+          <t>492829; 574832</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>761251; 1094074</t>
+          <t>1038257; 1148687</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>494083; 574991</t>
+          <t>490061; 578056</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>603682; 697331</t>
+          <t>601675; 696575</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>568059; 664023</t>
+          <t>564882; 667564</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1272239; 1826627</t>
+          <t>1296631; 1403302</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933527; 1045896</t>
+          <t>932541; 1048028</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1180465; 1318056</t>
+          <t>1188590; 1322663</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1085633; 1210414</t>
+          <t>1088262; 1210238</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2207379; 2865676</t>
+          <t>2365011; 2513361</t>
         </is>
       </c>
     </row>
